--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-rencontre.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-rencontre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T14:14:01+00:00</t>
+    <t>2026-10-06T20:02:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-rencontre.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-rencontre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T20:02:10+00:00</t>
+    <t>2026-10-07T08:37:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-rencontre.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-rencontre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T08:37:44+00:00</t>
+    <t>2026-10-07T09:51:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-rencontre.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-rencontre.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$142</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$141</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4470" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4441" uniqueCount="492">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T09:51:04+00:00</t>
+    <t>2026-10-08T08:06:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1022,20 +1022,27 @@
     <t>Encounter.participant</t>
   </si>
   <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Participant2 {https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-participant-corps|0.1.0}
+</t>
+  </si>
+  <si>
+    <t>Lieu d'exécution [0..1] et autres participants (FR-Participant) [0..*]</t>
+  </si>
+  <si>
+    <t>value:typeCode}
+value:participantRole.classCode}</t>
+  </si>
+  <si>
+    <t>Encounter.participant:lieuExecution</t>
+  </si>
+  <si>
+    <t>lieuExecution</t>
+  </si>
+  <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Participant2
 </t>
   </si>
   <si>
-    <t xml:space="preserve">value:typeCode}
-</t>
-  </si>
-  <si>
-    <t>Encounter.participant:lieuExecution</t>
-  </si>
-  <si>
-    <t>lieuExecution</t>
-  </si>
-  <si>
     <t>Lieu d'exécution</t>
   </si>
   <si>
@@ -1499,16 +1506,6 @@
   </si>
   <si>
     <t>ParticipantRole.scopingEntity</t>
-  </si>
-  <si>
-    <t>Encounter.participant:autresParticipants</t>
-  </si>
-  <si>
-    <t>autresParticipants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Participant2 {https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-participant-corps|0.1.0}
-</t>
   </si>
   <si>
     <t>Encounter.entryRelationship</t>
@@ -1860,7 +1857,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK142"/>
+  <dimension ref="A1:AK141"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="77.77734375" customWidth="true" bestFit="true"/>
@@ -1890,7 +1887,7 @@
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="60.4765625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="27.1328125" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
@@ -10505,8 +10502,12 @@
       <c r="K85" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="L85" s="2"/>
-      <c r="M85" s="2"/>
+      <c r="L85" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>325</v>
+      </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -10544,7 +10545,7 @@
         <v>75</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AC85" s="2"/>
       <c r="AD85" t="s" s="2">
@@ -10574,13 +10575,13 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>323</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D86" t="s" s="2">
         <v>75</v>
@@ -10602,13 +10603,13 @@
         <v>75</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -10679,10 +10680,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10780,10 +10781,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10881,10 +10882,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10982,10 +10983,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11083,10 +11084,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11186,10 +11187,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11289,10 +11290,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11392,10 +11393,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11495,10 +11496,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11596,10 +11597,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11636,7 +11637,7 @@
         <v>75</v>
       </c>
       <c r="S96" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="T96" t="s" s="2">
         <v>75</v>
@@ -11655,7 +11656,7 @@
       </c>
       <c r="Y96" s="2"/>
       <c r="Z96" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>75</v>
@@ -11673,7 +11674,7 @@
         <v>75</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>76</v>
@@ -11693,10 +11694,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11730,7 +11731,7 @@
       </c>
       <c r="Q97" s="2"/>
       <c r="R97" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="S97" t="s" s="2">
         <v>75</v>
@@ -11752,7 +11753,7 @@
       </c>
       <c r="Y97" s="2"/>
       <c r="Z97" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>75</v>
@@ -11770,7 +11771,7 @@
         <v>75</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -11790,10 +11791,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11869,7 +11870,7 @@
         <v>75</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -11889,10 +11890,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11968,7 +11969,7 @@
         <v>75</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -11988,10 +11989,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12067,7 +12068,7 @@
         <v>75</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -12085,12 +12086,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12104,7 +12105,7 @@
         <v>76</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>173</v>
+        <v>75</v>
       </c>
       <c r="I101" t="s" s="2">
         <v>75</v>
@@ -12113,7 +12114,7 @@
         <v>75</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L101" s="2"/>
       <c r="M101" s="2"/>
@@ -12166,7 +12167,7 @@
         <v>75</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>76</v>
@@ -12186,10 +12187,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12287,10 +12288,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12388,10 +12389,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12489,10 +12490,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12590,10 +12591,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12693,10 +12694,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12796,10 +12797,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12899,10 +12900,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13002,10 +13003,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13103,10 +13104,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13114,7 +13115,7 @@
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G111" t="s" s="2">
         <v>76</v>
@@ -13136,14 +13137,14 @@
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="Q111" s="2"/>
       <c r="R111" t="s" s="2">
         <v>75</v>
       </c>
       <c r="S111" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="T111" t="s" s="2">
         <v>75</v>
@@ -13162,7 +13163,7 @@
       </c>
       <c r="Y111" s="2"/>
       <c r="Z111" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>75</v>
@@ -13180,7 +13181,7 @@
         <v>75</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
@@ -13198,12 +13199,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13217,7 +13218,7 @@
         <v>82</v>
       </c>
       <c r="H112" t="s" s="2">
-        <v>173</v>
+        <v>75</v>
       </c>
       <c r="I112" t="s" s="2">
         <v>75</v>
@@ -13229,10 +13230,10 @@
         <v>96</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -13283,7 +13284,7 @@
         <v>75</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -13303,10 +13304,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13329,7 +13330,7 @@
         <v>75</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
@@ -13382,7 +13383,7 @@
         <v>75</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -13402,10 +13403,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13461,7 +13462,7 @@
       </c>
       <c r="Y114" s="2"/>
       <c r="Z114" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>75</v>
@@ -13479,7 +13480,7 @@
         <v>75</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -13499,10 +13500,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13578,7 +13579,7 @@
         <v>75</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -13596,12 +13597,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13615,7 +13616,7 @@
         <v>82</v>
       </c>
       <c r="H116" t="s" s="2">
-        <v>173</v>
+        <v>75</v>
       </c>
       <c r="I116" t="s" s="2">
         <v>75</v>
@@ -13624,13 +13625,13 @@
         <v>75</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -13681,7 +13682,7 @@
         <v>75</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>81</v>
@@ -13699,12 +13700,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13718,7 +13719,7 @@
         <v>82</v>
       </c>
       <c r="H117" t="s" s="2">
-        <v>173</v>
+        <v>75</v>
       </c>
       <c r="I117" t="s" s="2">
         <v>75</v>
@@ -13730,10 +13731,10 @@
         <v>265</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -13784,7 +13785,7 @@
         <v>75</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>81</v>
@@ -13804,10 +13805,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13830,7 +13831,7 @@
         <v>75</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L118" s="2"/>
       <c r="M118" s="2"/>
@@ -13883,7 +13884,7 @@
         <v>75</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
@@ -13901,12 +13902,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -13920,7 +13921,7 @@
         <v>76</v>
       </c>
       <c r="H119" t="s" s="2">
-        <v>173</v>
+        <v>75</v>
       </c>
       <c r="I119" t="s" s="2">
         <v>75</v>
@@ -13929,7 +13930,7 @@
         <v>75</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="L119" s="2"/>
       <c r="M119" s="2"/>
@@ -13982,7 +13983,7 @@
         <v>75</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>81</v>
@@ -14002,10 +14003,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -14103,10 +14104,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -14204,10 +14205,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -14305,10 +14306,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14406,10 +14407,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14509,10 +14510,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14612,10 +14613,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14715,10 +14716,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -14818,10 +14819,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -14919,10 +14920,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -14952,14 +14953,14 @@
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="Q129" s="2"/>
       <c r="R129" t="s" s="2">
         <v>75</v>
       </c>
       <c r="S129" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="T129" t="s" s="2">
         <v>75</v>
@@ -14978,7 +14979,7 @@
       </c>
       <c r="Y129" s="2"/>
       <c r="Z129" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>75</v>
@@ -14996,7 +14997,7 @@
         <v>75</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>81</v>
@@ -15016,10 +15017,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -15053,7 +15054,7 @@
       </c>
       <c r="Q130" s="2"/>
       <c r="R130" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="S130" t="s" s="2">
         <v>75</v>
@@ -15075,7 +15076,7 @@
       </c>
       <c r="Y130" s="2"/>
       <c r="Z130" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>75</v>
@@ -15093,7 +15094,7 @@
         <v>75</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>81</v>
@@ -15113,10 +15114,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -15172,7 +15173,7 @@
       </c>
       <c r="Y131" s="2"/>
       <c r="Z131" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>75</v>
@@ -15190,7 +15191,7 @@
         <v>75</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>81</v>
@@ -15210,10 +15211,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -15236,7 +15237,7 @@
         <v>75</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="L132" s="2"/>
       <c r="M132" s="2"/>
@@ -15289,7 +15290,7 @@
         <v>75</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>81</v>
@@ -15309,10 +15310,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15335,13 +15336,13 @@
         <v>75</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -15392,7 +15393,7 @@
         <v>75</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>81</v>
@@ -15412,10 +15413,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -15438,11 +15439,11 @@
         <v>75</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="L134" s="2"/>
       <c r="M134" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -15493,7 +15494,7 @@
         <v>75</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>81</v>
@@ -15513,10 +15514,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -15592,7 +15593,7 @@
         <v>75</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>81</v>
@@ -15612,10 +15613,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -15638,7 +15639,7 @@
         <v>75</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="L136" s="2"/>
       <c r="M136" s="2"/>
@@ -15691,7 +15692,7 @@
         <v>75</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>81</v>
@@ -15709,16 +15710,14 @@
         <v>75</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="C137" t="s" s="2">
-        <v>481</v>
-      </c>
+        <v>482</v>
+      </c>
+      <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
         <v>75</v>
       </c>
@@ -15730,7 +15729,7 @@
         <v>82</v>
       </c>
       <c r="H137" t="s" s="2">
-        <v>173</v>
+        <v>75</v>
       </c>
       <c r="I137" t="s" s="2">
         <v>75</v>
@@ -15739,7 +15738,7 @@
         <v>75</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L137" s="2"/>
       <c r="M137" s="2"/>
@@ -15792,7 +15791,7 @@
         <v>75</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>323</v>
+        <v>482</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>81</v>
@@ -15812,10 +15811,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -15838,7 +15837,7 @@
         <v>75</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L138" s="2"/>
       <c r="M138" s="2"/>
@@ -15891,7 +15890,7 @@
         <v>75</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>81</v>
@@ -15911,10 +15910,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -15937,7 +15936,7 @@
         <v>75</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L139" s="2"/>
       <c r="M139" s="2"/>
@@ -15990,7 +15989,7 @@
         <v>75</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>81</v>
@@ -16010,10 +16009,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -16036,7 +16035,7 @@
         <v>75</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L140" s="2"/>
       <c r="M140" s="2"/>
@@ -16089,7 +16088,7 @@
         <v>75</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>81</v>
@@ -16109,10 +16108,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -16135,7 +16134,7 @@
         <v>75</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L141" s="2"/>
       <c r="M141" s="2"/>
@@ -16188,7 +16187,7 @@
         <v>75</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>81</v>
@@ -16206,107 +16205,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="142" hidden="true">
-      <c r="A142" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="B142" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="C142" s="2"/>
-      <c r="D142" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E142" s="2"/>
-      <c r="F142" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H142" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I142" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J142" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K142" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="L142" s="2"/>
-      <c r="M142" s="2"/>
-      <c r="N142" s="2"/>
-      <c r="O142" s="2"/>
-      <c r="P142" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q142" s="2"/>
-      <c r="R142" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S142" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T142" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U142" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V142" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W142" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X142" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y142" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z142" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA142" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB142" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC142" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD142" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE142" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF142" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="AG142" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI142" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ142" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK142" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AK142">
+  <autoFilter ref="A1:AK141">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -16316,7 +16216,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI141">
+  <conditionalFormatting sqref="A2:AI140">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-rencontre.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-rencontre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T08:06:17+00:00</t>
+    <t>2026-10-08T10:07:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-rencontre.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-rencontre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T10:07:19+00:00</t>
+    <t>2026-10-08T14:58:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-rencontre.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-rencontre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T14:58:47+00:00</t>
+    <t>2026-10-12T13:25:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-rencontre.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-rencontre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:25:25+00:00</t>
+    <t>2026-10-14T12:53:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
